--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/21.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/21.xlsx
@@ -426,13 +426,13 @@
         <v>-5.932821262502166</v>
       </c>
       <c r="E2">
-        <v>-33.83137324218839</v>
+        <v>-25.44269440039659</v>
       </c>
       <c r="F2">
-        <v>-6.198914477310423</v>
+        <v>-5.063734699127231</v>
       </c>
       <c r="G2">
-        <v>-22.16113141734347</v>
+        <v>-14.57052572585593</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.518097651025395</v>
       </c>
       <c r="E3">
-        <v>-33.85313029555824</v>
+        <v>-26.98609796863882</v>
       </c>
       <c r="F3">
-        <v>-6.2153302341317</v>
+        <v>-4.921381417690942</v>
       </c>
       <c r="G3">
-        <v>-21.87679716310979</v>
+        <v>-13.24153255763404</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.129123628834662</v>
       </c>
       <c r="E4">
-        <v>-33.95959924795258</v>
+        <v>-24.41678672785491</v>
       </c>
       <c r="F4">
-        <v>-5.978398104480778</v>
+        <v>-4.944001646359188</v>
       </c>
       <c r="G4">
-        <v>-21.67252471492655</v>
+        <v>-15.1836039275196</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.813429202129798</v>
       </c>
       <c r="E5">
-        <v>-34.42745174734403</v>
+        <v>-26.53717675483643</v>
       </c>
       <c r="F5">
-        <v>-6.153908447948923</v>
+        <v>-5.219922544557675</v>
       </c>
       <c r="G5">
-        <v>-21.99256850339167</v>
+        <v>-14.39553653947996</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.544440613432982</v>
       </c>
       <c r="E6">
-        <v>-34.67394790876655</v>
+        <v>-26.28290746777975</v>
       </c>
       <c r="F6">
-        <v>-6.213326413384329</v>
+        <v>-4.6734659646463</v>
       </c>
       <c r="G6">
-        <v>-21.83303058933913</v>
+        <v>-14.06700259022978</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.314065994620837</v>
       </c>
       <c r="E7">
-        <v>-35.43074648492842</v>
+        <v>-27.1781958360442</v>
       </c>
       <c r="F7">
-        <v>-6.026468264865233</v>
+        <v>-4.924148164816292</v>
       </c>
       <c r="G7">
-        <v>-21.63024945635467</v>
+        <v>-13.77374997579753</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.091123322005322</v>
       </c>
       <c r="E8">
-        <v>-35.58685656939484</v>
+        <v>-27.97590917486537</v>
       </c>
       <c r="F8">
-        <v>-5.845196626110617</v>
+        <v>-4.552679228541895</v>
       </c>
       <c r="G8">
-        <v>-21.6654175890288</v>
+        <v>-15.03403436456465</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.853472383517277</v>
       </c>
       <c r="E9">
-        <v>-35.8781302818052</v>
+        <v>-27.50853895795573</v>
       </c>
       <c r="F9">
-        <v>-5.967509214970979</v>
+        <v>-4.340902131811785</v>
       </c>
       <c r="G9">
-        <v>-21.36227537281638</v>
+        <v>-15.22267507323869</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.571982815761622</v>
       </c>
       <c r="E10">
-        <v>-36.58236912439704</v>
+        <v>-28.80462444674305</v>
       </c>
       <c r="F10">
-        <v>-5.817181240547938</v>
+        <v>-4.560202461294121</v>
       </c>
       <c r="G10">
-        <v>-21.32292696387552</v>
+        <v>-15.93186681682161</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.22666419552907</v>
       </c>
       <c r="E11">
-        <v>-36.66000075431054</v>
+        <v>-29.13211915850376</v>
       </c>
       <c r="F11">
-        <v>-5.981619625310265</v>
+        <v>-3.912035618197411</v>
       </c>
       <c r="G11">
-        <v>-20.89604988265644</v>
+        <v>-15.06565877795458</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.808148766953658</v>
       </c>
       <c r="E12">
-        <v>-37.42187122136099</v>
+        <v>-29.09875789048926</v>
       </c>
       <c r="F12">
-        <v>-5.787531486099535</v>
+        <v>-3.945476810248427</v>
       </c>
       <c r="G12">
-        <v>-20.88937587800453</v>
+        <v>-14.66029338527922</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.313328218585832</v>
       </c>
       <c r="E13">
-        <v>-37.66219507271106</v>
+        <v>-30.71036706999801</v>
       </c>
       <c r="F13">
-        <v>-5.644985195058394</v>
+        <v>-3.944093436685752</v>
       </c>
       <c r="G13">
-        <v>-20.32730426548243</v>
+        <v>-14.52764508190633</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.762197010170149</v>
       </c>
       <c r="E14">
-        <v>-37.88134604383826</v>
+        <v>-31.25853884862651</v>
       </c>
       <c r="F14">
-        <v>-5.744114265416605</v>
+        <v>-3.408714614052014</v>
       </c>
       <c r="G14">
-        <v>-20.2183644284873</v>
+        <v>-12.39631613369355</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.177704578375797</v>
       </c>
       <c r="E15">
-        <v>-38.76262331352297</v>
+        <v>-31.5582717504832</v>
       </c>
       <c r="F15">
-        <v>-5.489667135400889</v>
+        <v>-3.465223353168788</v>
       </c>
       <c r="G15">
-        <v>-19.51263273303881</v>
+        <v>-13.19620576301187</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.599851494486428</v>
       </c>
       <c r="E16">
-        <v>-38.5946169278384</v>
+        <v>-31.67175530911542</v>
       </c>
       <c r="F16">
-        <v>-5.556472481334461</v>
+        <v>-3.265400426428477</v>
       </c>
       <c r="G16">
-        <v>-19.50865261128721</v>
+        <v>-13.1144541278583</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.06563258763539556</v>
       </c>
       <c r="E17">
-        <v>-40.11809521044687</v>
+        <v>-32.9834074273041</v>
       </c>
       <c r="F17">
-        <v>-5.447419569490711</v>
+        <v>-3.112292451001642</v>
       </c>
       <c r="G17">
-        <v>-19.26283989816141</v>
+        <v>-12.9578906411494</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.390248548579943</v>
       </c>
       <c r="E18">
-        <v>-40.44209620451067</v>
+        <v>-35.16509487845345</v>
       </c>
       <c r="F18">
-        <v>-5.380275421289395</v>
+        <v>-3.042688879981414</v>
       </c>
       <c r="G18">
-        <v>-18.97279959963585</v>
+        <v>-12.30977063384164</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.7426741791171397</v>
       </c>
       <c r="E19">
-        <v>-41.09226280321393</v>
+        <v>-34.35338176223757</v>
       </c>
       <c r="F19">
-        <v>-5.313013644916881</v>
+        <v>-3.124600333872437</v>
       </c>
       <c r="G19">
-        <v>-18.454251750489</v>
+        <v>-11.67531035188585</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.980283031733467</v>
       </c>
       <c r="E20">
-        <v>-41.06110916627816</v>
+        <v>-33.16009716189838</v>
       </c>
       <c r="F20">
-        <v>-5.078444847466145</v>
+        <v>-2.145806380928958</v>
       </c>
       <c r="G20">
-        <v>-18.23703816447533</v>
+        <v>-11.33749546745478</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.098225340771316</v>
       </c>
       <c r="E21">
-        <v>-41.48820087112657</v>
+        <v>-35.18190683820693</v>
       </c>
       <c r="F21">
-        <v>-4.981701475227996</v>
+        <v>-2.033112794349905</v>
       </c>
       <c r="G21">
-        <v>-18.3919134626919</v>
+        <v>-12.43311831470429</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.104124420629745</v>
       </c>
       <c r="E22">
-        <v>-42.16380843680492</v>
+        <v>-35.2130016049806</v>
       </c>
       <c r="F22">
-        <v>-4.868936649052302</v>
+        <v>-2.495543926758312</v>
       </c>
       <c r="G22">
-        <v>-18.19088614263095</v>
+        <v>-10.89537711209208</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.008188974353215</v>
       </c>
       <c r="E23">
-        <v>-42.4681400040164</v>
+        <v>-35.25039095062493</v>
       </c>
       <c r="F23">
-        <v>-4.89452823159439</v>
+        <v>-1.161628868234685</v>
       </c>
       <c r="G23">
-        <v>-18.30133041971109</v>
+        <v>-11.27725223962338</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.8256529152657108</v>
       </c>
       <c r="E24">
-        <v>-42.96249313330074</v>
+        <v>-36.94368927275805</v>
       </c>
       <c r="F24">
-        <v>-4.748038911715923</v>
+        <v>-1.919691072823791</v>
       </c>
       <c r="G24">
-        <v>-17.80895359372237</v>
+        <v>-11.10005315052712</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.5738742378999261</v>
       </c>
       <c r="E25">
-        <v>-42.87147986269458</v>
+        <v>-37.90306913365306</v>
       </c>
       <c r="F25">
-        <v>-4.658270393009346</v>
+        <v>-1.828157303181849</v>
       </c>
       <c r="G25">
-        <v>-18.11932105980869</v>
+        <v>-12.01060197693771</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.2704176620682185</v>
       </c>
       <c r="E26">
-        <v>-43.11074631536385</v>
+        <v>-37.82370989090563</v>
       </c>
       <c r="F26">
-        <v>-4.668923197809347</v>
+        <v>-1.379862260502215</v>
       </c>
       <c r="G26">
-        <v>-17.89720532878519</v>
+        <v>-12.09940167600096</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.06435179331541625</v>
       </c>
       <c r="E27">
-        <v>-43.2050608435216</v>
+        <v>-37.01928082513108</v>
       </c>
       <c r="F27">
-        <v>-4.682525818930718</v>
+        <v>-1.885678307264844</v>
       </c>
       <c r="G27">
-        <v>-18.08714868241833</v>
+        <v>-11.49313036846236</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.4093832462706904</v>
       </c>
       <c r="E28">
-        <v>-43.21436006489635</v>
+        <v>-38.48912612582972</v>
       </c>
       <c r="F28">
-        <v>-4.575055917193718</v>
+        <v>-1.577626694246569</v>
       </c>
       <c r="G28">
-        <v>-18.11961472913826</v>
+        <v>-11.11999969638699</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.7443639854078848</v>
       </c>
       <c r="E29">
-        <v>-43.30903460673771</v>
+        <v>-36.91820075680587</v>
       </c>
       <c r="F29">
-        <v>-4.634098632195656</v>
+        <v>-1.337196369053624</v>
       </c>
       <c r="G29">
-        <v>-17.85766004655077</v>
+        <v>-10.80401149776934</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.049014906756134</v>
       </c>
       <c r="E30">
-        <v>-43.1523403491243</v>
+        <v>-38.01151023647773</v>
       </c>
       <c r="F30">
-        <v>-4.758516102626531</v>
+        <v>-1.818082698829001</v>
       </c>
       <c r="G30">
-        <v>-18.08553924324342</v>
+        <v>-11.13722610957407</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.307361034680633</v>
       </c>
       <c r="E31">
-        <v>-42.94437018032204</v>
+        <v>-38.67404183345893</v>
       </c>
       <c r="F31">
-        <v>-4.624786954220787</v>
+        <v>-1.689119976458966</v>
       </c>
       <c r="G31">
-        <v>-18.16333208458552</v>
+        <v>-12.99564437641237</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.504663847190021</v>
       </c>
       <c r="E32">
-        <v>-42.3782271525941</v>
+        <v>-38.64938655672417</v>
       </c>
       <c r="F32">
-        <v>-4.426670464330243</v>
+        <v>-2.042764931327325</v>
       </c>
       <c r="G32">
-        <v>-18.02291220794908</v>
+        <v>-10.98228682753709</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.631025193767019</v>
       </c>
       <c r="E33">
-        <v>-42.63284739638638</v>
+        <v>-38.48869592079899</v>
       </c>
       <c r="F33">
-        <v>-4.464158231143935</v>
+        <v>-1.851014444927295</v>
       </c>
       <c r="G33">
-        <v>-17.73047169585279</v>
+        <v>-10.97211504070281</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.680589141464284</v>
       </c>
       <c r="E34">
-        <v>-42.12051622529159</v>
+        <v>-35.85786536062087</v>
       </c>
       <c r="F34">
-        <v>-4.605510844757642</v>
+        <v>-2.09390336457175</v>
       </c>
       <c r="G34">
-        <v>-17.96123180507464</v>
+        <v>-11.46710700027441</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.651761192121474</v>
       </c>
       <c r="E35">
-        <v>-42.11663758730402</v>
+        <v>-36.26120521929905</v>
       </c>
       <c r="F35">
-        <v>-4.567721552209331</v>
+        <v>-1.788827247264331</v>
       </c>
       <c r="G35">
-        <v>-18.51838322586835</v>
+        <v>-12.06676008392761</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.547753227359214</v>
       </c>
       <c r="E36">
-        <v>-41.60276673504662</v>
+        <v>-36.39623525725977</v>
       </c>
       <c r="F36">
-        <v>-4.542289844575984</v>
+        <v>-1.830348334962253</v>
       </c>
       <c r="G36">
-        <v>-18.54094162408953</v>
+        <v>-12.31793431308154</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.376488638577241</v>
       </c>
       <c r="E37">
-        <v>-41.42577812116784</v>
+        <v>-36.30581521674861</v>
       </c>
       <c r="F37">
-        <v>-4.544452711864693</v>
+        <v>-1.985930643821251</v>
       </c>
       <c r="G37">
-        <v>-18.28682742041834</v>
+        <v>-11.73431655918935</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.150294337820946</v>
       </c>
       <c r="E38">
-        <v>-40.95717163085411</v>
+        <v>-35.43601310019934</v>
       </c>
       <c r="F38">
-        <v>-4.322492494651969</v>
+        <v>-1.840334304003001</v>
       </c>
       <c r="G38">
-        <v>-18.70226616328119</v>
+        <v>-11.85503270036132</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.8860139018149872</v>
       </c>
       <c r="E39">
-        <v>-40.92838185735035</v>
+        <v>-34.84143578417724</v>
       </c>
       <c r="F39">
-        <v>-4.400445180725013</v>
+        <v>-1.42941768363989</v>
       </c>
       <c r="G39">
-        <v>-18.56650398064839</v>
+        <v>-12.58339169968374</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.6017906701478222</v>
       </c>
       <c r="E40">
-        <v>-40.98368131769502</v>
+        <v>-34.20268320421032</v>
       </c>
       <c r="F40">
-        <v>-4.494115309898776</v>
+        <v>-1.826561867564057</v>
       </c>
       <c r="G40">
-        <v>-18.74200175636607</v>
+        <v>-11.38525036603094</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.317783815566903</v>
       </c>
       <c r="E41">
-        <v>-39.84785399556514</v>
+        <v>-35.45962682791234</v>
       </c>
       <c r="F41">
-        <v>-4.323630671463415</v>
+        <v>-1.768300303022959</v>
       </c>
       <c r="G41">
-        <v>-18.73408416874313</v>
+        <v>-11.58017133276975</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.05245286152798279</v>
       </c>
       <c r="E42">
-        <v>-39.310518855237</v>
+        <v>-32.56724745871021</v>
       </c>
       <c r="F42">
-        <v>-4.380184142419941</v>
+        <v>-1.842718345388258</v>
       </c>
       <c r="G42">
-        <v>-19.21887481048641</v>
+        <v>-11.68608260226551</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.1788206317462332</v>
       </c>
       <c r="E43">
-        <v>-39.25070903478069</v>
+        <v>-33.60297286290052</v>
       </c>
       <c r="F43">
-        <v>-4.459417484497713</v>
+        <v>-1.560753678618946</v>
       </c>
       <c r="G43">
-        <v>-18.70911899450809</v>
+        <v>-12.0836780622881</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.3627001005087703</v>
       </c>
       <c r="E44">
-        <v>-39.0929573784865</v>
+        <v>-32.44628286101732</v>
       </c>
       <c r="F44">
-        <v>-4.334887356100058</v>
+        <v>-1.735667597557075</v>
       </c>
       <c r="G44">
-        <v>-18.65125629291807</v>
+        <v>-11.90733209079731</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.4934123602123482</v>
       </c>
       <c r="E45">
-        <v>-38.3766410957162</v>
+        <v>-31.71547319718546</v>
       </c>
       <c r="F45">
-        <v>-4.584516701301092</v>
+        <v>-2.140252177493188</v>
       </c>
       <c r="G45">
-        <v>-18.97387255908579</v>
+        <v>-12.41502894024707</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.5676926665562267</v>
       </c>
       <c r="E46">
-        <v>-38.35772113131215</v>
+        <v>-29.52403594149759</v>
       </c>
       <c r="F46">
-        <v>-4.330258439053214</v>
+        <v>-1.930051463930605</v>
       </c>
       <c r="G46">
-        <v>-18.79529863815613</v>
+        <v>-12.74576951099598</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.5909667946739177</v>
       </c>
       <c r="E47">
-        <v>-37.54643822012699</v>
+        <v>-31.98846546002686</v>
       </c>
       <c r="F47">
-        <v>-4.244789147167166</v>
+        <v>-2.130061601703948</v>
       </c>
       <c r="G47">
-        <v>-19.29015934886534</v>
+        <v>-11.96248286276845</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.5713701987598707</v>
       </c>
       <c r="E48">
-        <v>-37.70336116567778</v>
+        <v>-30.23562449740389</v>
       </c>
       <c r="F48">
-        <v>-4.235273690811209</v>
+        <v>-1.563321617567624</v>
       </c>
       <c r="G48">
-        <v>-19.17630588258495</v>
+        <v>-11.11533708055102</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.5222943127710787</v>
       </c>
       <c r="E49">
-        <v>-36.7693181168557</v>
+        <v>-29.3125018636513</v>
       </c>
       <c r="F49">
-        <v>-4.345704177645814</v>
+        <v>-1.757380763919256</v>
       </c>
       <c r="G49">
-        <v>-18.93103457101646</v>
+        <v>-11.76358505549959</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.4582067980401918</v>
       </c>
       <c r="E50">
-        <v>-36.37524578023422</v>
+        <v>-27.41537919066994</v>
       </c>
       <c r="F50">
-        <v>-4.356017351810667</v>
+        <v>-2.058041682969753</v>
       </c>
       <c r="G50">
-        <v>-19.09525806945589</v>
+        <v>-11.52254980096434</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.3932216523994296</v>
       </c>
       <c r="E51">
-        <v>-36.23002893999325</v>
+        <v>-28.63544518629049</v>
       </c>
       <c r="F51">
-        <v>-4.456211702648879</v>
+        <v>-2.057279584959178</v>
       </c>
       <c r="G51">
-        <v>-19.58425523723837</v>
+        <v>-12.03410864818957</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.3406873700153026</v>
       </c>
       <c r="E52">
-        <v>-35.78745664674962</v>
+        <v>-26.79995051607952</v>
       </c>
       <c r="F52">
-        <v>-4.288528602769786</v>
+        <v>-1.273648992115263</v>
       </c>
       <c r="G52">
-        <v>-19.48136597279887</v>
+        <v>-11.70700695215009</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.3097860423954866</v>
       </c>
       <c r="E53">
-        <v>-35.37383715207402</v>
+        <v>-27.93662013437482</v>
       </c>
       <c r="F53">
-        <v>-4.355499622183918</v>
+        <v>-2.193192309838701</v>
       </c>
       <c r="G53">
-        <v>-19.15173117371549</v>
+        <v>-12.83243641604559</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.305991048223418</v>
       </c>
       <c r="E54">
-        <v>-35.00240492125389</v>
+        <v>-27.04370015801639</v>
       </c>
       <c r="F54">
-        <v>-4.293263550844189</v>
+        <v>-1.803969803387506</v>
       </c>
       <c r="G54">
-        <v>-19.55504416230542</v>
+        <v>-12.05384519586963</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.3294485439115287</v>
       </c>
       <c r="E55">
-        <v>-34.89265056096698</v>
+        <v>-26.62956668154093</v>
       </c>
       <c r="F55">
-        <v>-4.316022945236105</v>
+        <v>-1.90623341599791</v>
       </c>
       <c r="G55">
-        <v>-19.40602256335089</v>
+        <v>-12.61826780363907</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.3754964001344606</v>
       </c>
       <c r="E56">
-        <v>-34.42663435778564</v>
+        <v>-25.74009740237634</v>
       </c>
       <c r="F56">
-        <v>-4.375160094121961</v>
+        <v>-2.123006396534305</v>
       </c>
       <c r="G56">
-        <v>-19.47629156365718</v>
+        <v>-11.90421493031583</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.4350781197540734</v>
       </c>
       <c r="E57">
-        <v>-34.09520440211227</v>
+        <v>-25.6496909472872</v>
       </c>
       <c r="F57">
-        <v>-4.439785177051365</v>
+        <v>-1.646934538103998</v>
       </c>
       <c r="G57">
-        <v>-19.66276010365887</v>
+        <v>-12.35294494712081</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.4962239802687107</v>
       </c>
       <c r="E58">
-        <v>-33.60977236662304</v>
+        <v>-24.51661240887999</v>
       </c>
       <c r="F58">
-        <v>-4.346492783413279</v>
+        <v>-1.957989811324824</v>
       </c>
       <c r="G58">
-        <v>-19.84140621146284</v>
+        <v>-12.56855729701349</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.5451743297008208</v>
       </c>
       <c r="E59">
-        <v>-33.69314383734125</v>
+        <v>-24.22432658252891</v>
       </c>
       <c r="F59">
-        <v>-4.549309429947307</v>
+        <v>-1.848641172318275</v>
       </c>
       <c r="G59">
-        <v>-19.87827565751554</v>
+        <v>-12.06253387055904</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.5700090589319616</v>
       </c>
       <c r="E60">
-        <v>-33.22603174345006</v>
+        <v>-22.6818151236662</v>
       </c>
       <c r="F60">
-        <v>-4.412253558051921</v>
+        <v>-1.932643425533964</v>
       </c>
       <c r="G60">
-        <v>-19.77716153393969</v>
+        <v>-12.33176794317616</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.5600323782186943</v>
       </c>
       <c r="E61">
-        <v>-33.36405057425583</v>
+        <v>-24.00192869553821</v>
       </c>
       <c r="F61">
-        <v>-4.590332668836147</v>
+        <v>-2.473612899769195</v>
       </c>
       <c r="G61">
-        <v>-20.24966728216441</v>
+        <v>-12.80950723978819</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.5097247597637201</v>
       </c>
       <c r="E62">
-        <v>-32.85608258786743</v>
+        <v>-24.12564207695376</v>
       </c>
       <c r="F62">
-        <v>-4.779299012395367</v>
+        <v>-1.969672276806505</v>
       </c>
       <c r="G62">
-        <v>-20.18578517962358</v>
+        <v>-12.61436643120489</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.4169748474484793</v>
       </c>
       <c r="E63">
-        <v>-32.97713549080348</v>
+        <v>-22.78546283675376</v>
       </c>
       <c r="F63">
-        <v>-4.790852252562212</v>
+        <v>-2.239166700694074</v>
       </c>
       <c r="G63">
-        <v>-20.07692081072432</v>
+        <v>-13.52811116741438</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.285881172773435</v>
       </c>
       <c r="E64">
-        <v>-32.68464361888505</v>
+        <v>-23.41918654633516</v>
       </c>
       <c r="F64">
-        <v>-4.772567698880219</v>
+        <v>-1.715801690503138</v>
       </c>
       <c r="G64">
-        <v>-20.69850886050241</v>
+        <v>-14.04303982918116</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.1245196277694559</v>
       </c>
       <c r="E65">
-        <v>-32.21469670026505</v>
+        <v>-21.69685844157587</v>
       </c>
       <c r="F65">
-        <v>-4.749467017118349</v>
+        <v>-2.57456852025058</v>
       </c>
       <c r="G65">
-        <v>-20.12087605473464</v>
+        <v>-13.5620422795606</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.05530428296662471</v>
       </c>
       <c r="E66">
-        <v>-32.64161179462717</v>
+        <v>-21.29194946665404</v>
       </c>
       <c r="F66">
-        <v>-4.965701558842923</v>
+        <v>-2.234689374881942</v>
       </c>
       <c r="G66">
-        <v>-20.24964431361349</v>
+        <v>-13.85571489035246</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.2395249677403259</v>
       </c>
       <c r="E67">
-        <v>-32.17702432499524</v>
+        <v>-21.24132112724828</v>
       </c>
       <c r="F67">
-        <v>-5.078885538924434</v>
+        <v>-3.241142515404897</v>
       </c>
       <c r="G67">
-        <v>-20.2709952223008</v>
+        <v>-13.39325952376432</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.4135400246673411</v>
       </c>
       <c r="E68">
-        <v>-32.01055535623627</v>
+        <v>-22.34102481221896</v>
       </c>
       <c r="F68">
-        <v>-4.951073418876887</v>
+        <v>-2.507079771209698</v>
       </c>
       <c r="G68">
-        <v>-20.37155810065466</v>
+        <v>-13.43740835984665</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.5621939249494518</v>
       </c>
       <c r="E69">
-        <v>-31.34008987279364</v>
+        <v>-21.60903321667111</v>
       </c>
       <c r="F69">
-        <v>-4.974430894533625</v>
+        <v>-3.048112201367542</v>
       </c>
       <c r="G69">
-        <v>-20.52688292622487</v>
+        <v>-12.98935755590447</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.6727833225630063</v>
       </c>
       <c r="E70">
-        <v>-32.13127088785875</v>
+        <v>-21.77419572067887</v>
       </c>
       <c r="F70">
-        <v>-5.123558564590009</v>
+        <v>-2.984422345235899</v>
       </c>
       <c r="G70">
-        <v>-20.30024075006013</v>
+        <v>-11.51176442569845</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.735256130045789</v>
       </c>
       <c r="E71">
-        <v>-31.87438640706263</v>
+        <v>-20.21374697627177</v>
       </c>
       <c r="F71">
-        <v>-5.139982605085314</v>
+        <v>-2.855755350028663</v>
       </c>
       <c r="G71">
-        <v>-20.35979984319639</v>
+        <v>-13.38881018732971</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.743371433096087</v>
       </c>
       <c r="E72">
-        <v>-31.77812237084458</v>
+        <v>-20.00628852503237</v>
       </c>
       <c r="F72">
-        <v>-5.309713429184127</v>
+        <v>-3.286074820067548</v>
       </c>
       <c r="G72">
-        <v>-19.98124367127247</v>
+        <v>-13.50394497062907</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.6962352749911542</v>
       </c>
       <c r="E73">
-        <v>-32.0790553183133</v>
+        <v>-21.06430307828845</v>
       </c>
       <c r="F73">
-        <v>-5.386207360260842</v>
+        <v>-3.300038609376539</v>
       </c>
       <c r="G73">
-        <v>-19.92308401913131</v>
+        <v>-13.25739726387395</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.5982184634489052</v>
       </c>
       <c r="E74">
-        <v>-32.08077613843621</v>
+        <v>-21.61540930807391</v>
       </c>
       <c r="F74">
-        <v>-5.334830357204411</v>
+        <v>-3.405265292186757</v>
       </c>
       <c r="G74">
-        <v>-20.30047371679085</v>
+        <v>-12.38867088746005</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.4579085221227507</v>
       </c>
       <c r="E75">
-        <v>-32.25481671573601</v>
+        <v>-21.09124297016008</v>
       </c>
       <c r="F75">
-        <v>-5.31999678212248</v>
+        <v>-3.52428512062099</v>
       </c>
       <c r="G75">
-        <v>-19.95199486229158</v>
+        <v>-13.36518211088015</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.2862099083768586</v>
       </c>
       <c r="E76">
-        <v>-32.58286163708866</v>
+        <v>-20.92078215156335</v>
       </c>
       <c r="F76">
-        <v>-5.374570454986315</v>
+        <v>-3.882324564561201</v>
       </c>
       <c r="G76">
-        <v>-19.84017739398882</v>
+        <v>-13.00126182772214</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.09518807321961525</v>
       </c>
       <c r="E77">
-        <v>-32.69938153754301</v>
+        <v>-22.23579666170273</v>
       </c>
       <c r="F77">
-        <v>-5.418888111036088</v>
+        <v>-3.706602159037939</v>
       </c>
       <c r="G77">
-        <v>-19.68815347730741</v>
+        <v>-11.98983184446642</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.1015444048828653</v>
       </c>
       <c r="E78">
-        <v>-32.45945166343162</v>
+        <v>-22.13328106711709</v>
       </c>
       <c r="F78">
-        <v>-5.462542244796219</v>
+        <v>-3.754522384922488</v>
       </c>
       <c r="G78">
-        <v>-19.18129169874453</v>
+        <v>-11.52935505447863</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.291612862887882</v>
       </c>
       <c r="E79">
-        <v>-32.9671094493505</v>
+        <v>-24.01553675993127</v>
       </c>
       <c r="F79">
-        <v>-5.687770371412988</v>
+        <v>-3.826005521579668</v>
       </c>
       <c r="G79">
-        <v>-19.29130777641115</v>
+        <v>-11.70296448718885</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.4629757003761692</v>
       </c>
       <c r="E80">
-        <v>-33.36953002780512</v>
+        <v>-23.92679678327696</v>
       </c>
       <c r="F80">
-        <v>-5.51700243132587</v>
+        <v>-4.009399437620257</v>
       </c>
       <c r="G80">
-        <v>-18.75733490471335</v>
+        <v>-11.51435987195197</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.6051544685903135</v>
       </c>
       <c r="E81">
-        <v>-33.76814442385629</v>
+        <v>-23.59964170706682</v>
       </c>
       <c r="F81">
-        <v>-5.604226205371047</v>
+        <v>-3.487611638964251</v>
       </c>
       <c r="G81">
-        <v>-18.75720529646176</v>
+        <v>-11.57551199815534</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.7099842132561504</v>
       </c>
       <c r="E82">
-        <v>-33.89929808806644</v>
+        <v>-23.44049301654125</v>
       </c>
       <c r="F82">
-        <v>-5.492088453319272</v>
+        <v>-3.993491470016895</v>
       </c>
       <c r="G82">
-        <v>-18.44781727501093</v>
+        <v>-11.24746202908518</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.7702882732486473</v>
       </c>
       <c r="E83">
-        <v>-34.52536188386387</v>
+        <v>-23.08102274981238</v>
       </c>
       <c r="F83">
-        <v>-5.802333583220159</v>
+        <v>-4.019819471180072</v>
       </c>
       <c r="G83">
-        <v>-18.30752864723688</v>
+        <v>-10.68168427681168</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.7809714911489933</v>
       </c>
       <c r="E84">
-        <v>-34.95619410824262</v>
+        <v>-24.55908043812392</v>
       </c>
       <c r="F84">
-        <v>-5.775771982449394</v>
+        <v>-3.758170514964417</v>
       </c>
       <c r="G84">
-        <v>-18.3631994928252</v>
+        <v>-11.07451212190841</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.7394773033442367</v>
       </c>
       <c r="E85">
-        <v>-35.72685434334197</v>
+        <v>-24.85658306653183</v>
       </c>
       <c r="F85">
-        <v>-5.75978946177978</v>
+        <v>-4.713648410621298</v>
       </c>
       <c r="G85">
-        <v>-18.19788334760647</v>
+        <v>-10.92272609379005</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.6437088720036683</v>
       </c>
       <c r="E86">
-        <v>-36.39310834595747</v>
+        <v>-27.54640605760787</v>
       </c>
       <c r="F86">
-        <v>-5.770279906568833</v>
+        <v>-4.194296012129523</v>
       </c>
       <c r="G86">
-        <v>-17.94920120622693</v>
+        <v>-10.72635810834352</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.4957503680537131</v>
       </c>
       <c r="E87">
-        <v>-36.89003364847817</v>
+        <v>-29.48207962981653</v>
       </c>
       <c r="F87">
-        <v>-5.916591127455698</v>
+        <v>-4.312883432779494</v>
       </c>
       <c r="G87">
-        <v>-17.6786497231537</v>
+        <v>-9.944167388116854</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.2961521597190646</v>
       </c>
       <c r="E88">
-        <v>-37.99353219466728</v>
+        <v>-30.16905592949113</v>
       </c>
       <c r="F88">
-        <v>-5.795632090931512</v>
+        <v>-4.231363796669995</v>
       </c>
       <c r="G88">
-        <v>-17.80344770394562</v>
+        <v>-11.10827261053353</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.04864769778631462</v>
       </c>
       <c r="E89">
-        <v>-38.67184778780221</v>
+        <v>-32.042275052423</v>
       </c>
       <c r="F89">
-        <v>-5.948314285513308</v>
+        <v>-4.441959641483714</v>
       </c>
       <c r="G89">
-        <v>-17.59974290709217</v>
+        <v>-9.498377345829136</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.2421313766853671</v>
       </c>
       <c r="E90">
-        <v>-39.78004236153728</v>
+        <v>-32.22902026355131</v>
       </c>
       <c r="F90">
-        <v>-5.937191796395919</v>
+        <v>-4.147631591227618</v>
       </c>
       <c r="G90">
-        <v>-17.54028717243504</v>
+        <v>-9.125466515598244</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.5724055763275075</v>
       </c>
       <c r="E91">
-        <v>-40.41689524665799</v>
+        <v>-35.1638835116564</v>
       </c>
       <c r="F91">
-        <v>-6.273569432752923</v>
+        <v>-4.616230747317271</v>
       </c>
       <c r="G91">
-        <v>-17.36589352777211</v>
+        <v>-9.932181085760202</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.9332627429207005</v>
       </c>
       <c r="E92">
-        <v>-41.68106857911325</v>
+        <v>-34.40256325419787</v>
       </c>
       <c r="F92">
-        <v>-6.124537024947861</v>
+        <v>-4.891558534455354</v>
       </c>
       <c r="G92">
-        <v>-17.05458271048745</v>
+        <v>-10.44067199082735</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.321397898163894</v>
       </c>
       <c r="E93">
-        <v>-42.92201310414617</v>
+        <v>-34.93533822120029</v>
       </c>
       <c r="F93">
-        <v>-6.144998528164411</v>
+        <v>-5.522152391469074</v>
       </c>
       <c r="G93">
-        <v>-18.03207501915383</v>
+        <v>-10.32136349370438</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.725119565098427</v>
       </c>
       <c r="E94">
-        <v>-44.4512493414554</v>
+        <v>-37.2582800978339</v>
       </c>
       <c r="F94">
-        <v>-6.257124683072547</v>
+        <v>-5.174740072939379</v>
       </c>
       <c r="G94">
-        <v>-17.78891681426962</v>
+        <v>-9.940751636473474</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.139724889272349</v>
       </c>
       <c r="E95">
-        <v>-45.20271111099923</v>
+        <v>-39.99491845320124</v>
       </c>
       <c r="F95">
-        <v>-6.31477242736817</v>
+        <v>-4.791007157266535</v>
       </c>
       <c r="G95">
-        <v>-18.20253776038854</v>
+        <v>-9.982022841248169</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.554724298799938</v>
       </c>
       <c r="E96">
-        <v>-46.9124523222542</v>
+        <v>-40.31325206204443</v>
       </c>
       <c r="F96">
-        <v>-6.513171390543069</v>
+        <v>-5.838244138498921</v>
       </c>
       <c r="G96">
-        <v>-18.13690840736731</v>
+        <v>-9.852578650728075</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.958943383616538</v>
       </c>
       <c r="E97">
-        <v>-48.07355532205789</v>
+        <v>-43.04876962009487</v>
       </c>
       <c r="F97">
-        <v>-6.548519484355329</v>
+        <v>-5.209048565661126</v>
       </c>
       <c r="G97">
-        <v>-18.70022196224966</v>
+        <v>-10.60435900954181</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.342133915266857</v>
       </c>
       <c r="E98">
-        <v>-49.32626708679974</v>
+        <v>-45.2728866084591</v>
       </c>
       <c r="F98">
-        <v>-6.505491182168013</v>
+        <v>-5.358906027399376</v>
       </c>
       <c r="G98">
-        <v>-18.86063924368013</v>
+        <v>-11.68161685972311</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.68579985530029</v>
       </c>
       <c r="E99">
-        <v>-50.89758530094375</v>
+        <v>-46.75370213744131</v>
       </c>
       <c r="F99">
-        <v>-6.553706306847958</v>
+        <v>-5.4683656676379</v>
       </c>
       <c r="G99">
-        <v>-18.57689889054871</v>
+        <v>-11.37289656685963</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.980503003374287</v>
       </c>
       <c r="E100">
-        <v>-52.34104771207369</v>
+        <v>-47.80760710053542</v>
       </c>
       <c r="F100">
-        <v>-6.758200397372655</v>
+        <v>-5.446519962491271</v>
       </c>
       <c r="G100">
-        <v>-19.07094749892196</v>
+        <v>-12.01589786853465</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.202007761376821</v>
       </c>
       <c r="E101">
-        <v>-54.11750240240966</v>
+        <v>-49.89557778209604</v>
       </c>
       <c r="F101">
-        <v>-6.598370634655804</v>
+        <v>-5.384067687259411</v>
       </c>
       <c r="G101">
-        <v>-19.33138133531665</v>
+        <v>-12.82898785218661</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.347143709191623</v>
       </c>
       <c r="E102">
-        <v>-55.55610123245537</v>
+        <v>-51.58174488978558</v>
       </c>
       <c r="F102">
-        <v>-6.850107346529559</v>
+        <v>-5.24857577302051</v>
       </c>
       <c r="G102">
-        <v>-19.37824210101786</v>
+        <v>-11.56088431244334</v>
       </c>
     </row>
   </sheetData>
